--- a/data/trans_dic/P17G_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,04</t>
+          <t>2,23; 5,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,51</t>
+          <t>1,67; 5,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,6</t>
+          <t>2,88; 7,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,02</t>
+          <t>3,48; 7,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,73</t>
+          <t>1,75; 6,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,68</t>
+          <t>2,59; 7,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,61</t>
+          <t>2,82; 7,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,19</t>
+          <t>4,4; 8,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,2</t>
+          <t>2,4; 5,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,41</t>
+          <t>2,56; 5,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,48</t>
+          <t>3,38; 6,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,25</t>
+          <t>4,39; 7,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,1</t>
+          <t>0,55; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,64</t>
+          <t>2,97; 7,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,69</t>
+          <t>2,53; 6,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,67</t>
+          <t>2,26; 5,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,06</t>
+          <t>1,27; 4,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,65</t>
+          <t>1,19; 5,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,11</t>
+          <t>1,06; 4,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,92</t>
+          <t>3,16; 6,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,4</t>
+          <t>1,2; 3,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,1</t>
+          <t>2,55; 5,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,71</t>
+          <t>2,06; 4,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,75</t>
+          <t>3,06; 5,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,91</t>
+          <t>0,67; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,97</t>
+          <t>0,45; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,15</t>
+          <t>0,69; 6,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,65</t>
+          <t>0,41; 3,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,46</t>
+          <t>0,58; 5,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,35</t>
+          <t>1,07; 5,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,09</t>
+          <t>0,98; 3,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,5</t>
+          <t>0,33; 1,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,78</t>
+          <t>0,66; 2,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,27</t>
+          <t>0,18; 1,29</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,65</t>
+          <t>0,45; 1,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,83</t>
+          <t>0,42; 1,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,08</t>
+          <t>0,51; 2,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,54</t>
+          <t>0,73; 2,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,81; 2,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,68</t>
+          <t>0,3; 1,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,8</t>
+          <t>0,71; 1,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,49</t>
+          <t>0,05; 0,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,82</t>
+          <t>0,69; 1,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,53</t>
+          <t>0,51; 1,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,88</t>
+          <t>0,34; 2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,91</t>
+          <t>0,19; 1,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,2</t>
+          <t>0,45; 2,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,35</t>
+          <t>0,4; 1,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,5</t>
+          <t>0,21; 1,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,67</t>
+          <t>0,53; 1,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,0</t>
+          <t>0,28; 1,0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,69</t>
+          <t>0,76; 5,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,7</t>
+          <t>0,3; 2,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,15</t>
+          <t>0,76; 2,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,86</t>
+          <t>0,56; 1,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,77</t>
+          <t>0,92; 2,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,57</t>
+          <t>0,81; 2,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,83</t>
+          <t>0,68; 1,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,06</t>
+          <t>0,81; 2,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,31</t>
+          <t>0,88; 2,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,77</t>
+          <t>0,8; 2,85</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,93</t>
+          <t>1,05; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,77</t>
+          <t>0,93; 1,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,36</t>
+          <t>1,37; 2,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,29</t>
+          <t>1,27; 2,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,14</t>
+          <t>1,22; 2,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,65</t>
+          <t>0,88; 1,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,42</t>
+          <t>1,37; 2,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,59</t>
+          <t>1,65; 2,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,86</t>
+          <t>1,25; 1,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,59</t>
+          <t>1,01; 1,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,2</t>
+          <t>1,54; 2,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,34</t>
+          <t>1,62; 2,34</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10225; 28624</t>
+          <t>10555; 28109</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7448; 23945</t>
+          <t>7267; 23825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12790; 32625</t>
+          <t>12343; 31653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17431; 40502</t>
+          <t>17558; 38705</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5124; 17586</t>
+          <t>5361; 18579</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7925; 23798</t>
+          <t>8024; 23397</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9985; 26333</t>
+          <t>9760; 26235</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19636; 36636</t>
+          <t>19669; 36847</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18817; 40619</t>
+          <t>18699; 39333</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18065; 40233</t>
+          <t>19067; 41166</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25928; 50220</t>
+          <t>26173; 51531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41313; 69051</t>
+          <t>41850; 70004</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025; 11392</t>
+          <t>2011; 11959</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12397; 31793</t>
+          <t>12333; 31823</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9466; 25153</t>
+          <t>9510; 25614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9977; 25644</t>
+          <t>10206; 26034</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4543; 18815</t>
+          <t>4714; 17275</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3904; 18729</t>
+          <t>3932; 19813</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3963; 15209</t>
+          <t>3921; 15157</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12739; 26487</t>
+          <t>12094; 25970</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8980; 25108</t>
+          <t>8898; 25998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20301; 45567</t>
+          <t>19085; 42938</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15322; 35153</t>
+          <t>15367; 34450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25039; 47982</t>
+          <t>25536; 47069</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3700; 15784</t>
+          <t>3612; 15793</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6683</t>
+          <t>0; 6457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2357; 15437</t>
+          <t>2338; 14886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4135</t>
+          <t>0; 4805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1151; 10322</t>
+          <t>1164; 10627</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1043; 9390</t>
+          <t>1048; 10266</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>957; 8950</t>
+          <t>954; 8972</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1837; 8913</t>
+          <t>1784; 8673</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6697; 21953</t>
+          <t>6925; 21802</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2866; 13269</t>
+          <t>2907; 12309</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4620; 19004</t>
+          <t>4513; 18147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1711; 10629</t>
+          <t>1511; 10808</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6173; 20324</t>
+          <t>5579; 21746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6602</t>
+          <t>0; 6550</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4560; 20956</t>
+          <t>4835; 21868</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4948; 21542</t>
+          <t>5285; 21932</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5280; 18062</t>
+          <t>5212; 18458</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6615</t>
+          <t>0; 6671</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6454; 20924</t>
+          <t>6645; 21451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3085; 16382</t>
+          <t>2892; 16093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13942; 35108</t>
+          <t>13860; 33759</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>952; 9337</t>
+          <t>954; 9509</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14233; 35850</t>
+          <t>13598; 35251</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10266; 30831</t>
+          <t>10331; 32042</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5248</t>
+          <t>0; 6195</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2083; 11611</t>
+          <t>2092; 12717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 4587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1067; 10860</t>
+          <t>1060; 11206</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7446</t>
+          <t>0; 6669</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3224; 16103</t>
+          <t>3323; 15827</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3449; 11313</t>
+          <t>3333; 11740</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1960; 13756</t>
+          <t>1912; 12527</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7292</t>
+          <t>0; 7715</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7575; 22537</t>
+          <t>7182; 22975</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3947; 13111</t>
+          <t>3720; 13138</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>0; 4809</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1967; 15016</t>
+          <t>2000; 15182</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>851; 7730</t>
+          <t>868; 8456</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 17493</t>
+          <t>0; 17821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9919; 26884</t>
+          <t>9494; 25398</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5772; 20494</t>
+          <t>6186; 20525</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9890; 29790</t>
+          <t>9908; 28167</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6061; 19560</t>
+          <t>6123; 18795</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10920; 28293</t>
+          <t>10460; 26643</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10706; 28083</t>
+          <t>11058; 29231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12059; 31465</t>
+          <t>11978; 32518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7930; 27765</t>
+          <t>7971; 28542</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34575; 62841</t>
+          <t>34226; 61826</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31344; 59979</t>
+          <t>31544; 62169</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47675; 79541</t>
+          <t>46136; 79126</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40112; 77315</t>
+          <t>42903; 79946</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>42683; 72324</t>
+          <t>41157; 72498</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31201; 58069</t>
+          <t>30899; 59842</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51033; 85090</t>
+          <t>47980; 83256</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58519; 92738</t>
+          <t>59086; 92920</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>82133; 123443</t>
+          <t>83215; 125992</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70371; 109742</t>
+          <t>69874; 111509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103406; 151654</t>
+          <t>106136; 153681</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>112004; 162346</t>
+          <t>112580; 162361</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,93</t>
+          <t>2,25; 6,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,49</t>
+          <t>1,68; 5,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,38</t>
+          <t>2,78; 7,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,66</t>
+          <t>3,52; 7,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,06</t>
+          <t>1,56; 5,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,55</t>
+          <t>2,49; 7,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,58</t>
+          <t>2,86; 7,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,23</t>
+          <t>4,49; 8,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,04</t>
+          <t>2,44; 5,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,53</t>
+          <t>2,53; 5,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,65</t>
+          <t>3,34; 6,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,35</t>
+          <t>4,36; 7,02</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -857,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,26</t>
+          <t>0,76; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,65</t>
+          <t>3,05; 7,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,81</t>
+          <t>2,53; 6,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,76</t>
+          <t>2,38; 5,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,65</t>
+          <t>1,21; 4,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,98</t>
+          <t>1,19; 5,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,1</t>
+          <t>1,04; 4,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,79</t>
+          <t>3,35; 7,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,75</t>
+          <t>2,53; 5,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,62</t>
+          <t>2,09; 4,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,64</t>
+          <t>3,13; 5,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,91</t>
+          <t>0,66; 2,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,86</t>
+          <t>0,45; 2,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,33</t>
+          <t>0,81; 6,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,99</t>
+          <t>0,4; 3,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,47</t>
+          <t>0,58; 5,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,21</t>
+          <t>1,03; 4,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,07</t>
+          <t>0,97; 3,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,4</t>
+          <t>0,24; 1,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,65</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,29</t>
+          <t>0,47; 1,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,76</t>
+          <t>0,52; 1,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,91</t>
+          <t>0,4; 1,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,12</t>
+          <t>0,45; 2,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,59</t>
+          <t>0,72; 2,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,61</t>
+          <t>0,77; 2,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,65</t>
+          <t>0,56; 1,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,73</t>
+          <t>0,69; 1,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,79</t>
+          <t>0,71; 1,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,59</t>
+          <t>0,59; 1,66</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,59 +1287,59 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,06</t>
+          <t>0,34; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,97</t>
+          <t>0,19; 2,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,16</t>
+          <t>0,43; 2,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,4</t>
+          <t>0,44; 1,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,37</t>
+          <t>0,22; 1,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,7</t>
+          <t>0,56; 1,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,0</t>
+          <t>0,29; 0,89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,75</t>
+          <t>0,75; 5,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,95</t>
+          <t>0,3; 2,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 6,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,03</t>
+          <t>0,81; 2,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,86</t>
+          <t>0,63; 1,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,62</t>
+          <t>0,92; 2,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,47</t>
+          <t>0,8; 2,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,72</t>
+          <t>0,7; 1,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,14</t>
+          <t>0,8; 2,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,39</t>
+          <t>0,82; 2,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,85</t>
+          <t>0,73; 2,44</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,89</t>
+          <t>1,04; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,83</t>
+          <t>0,91; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,35</t>
+          <t>1,39; 2,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,37</t>
+          <t>1,42; 2,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,15</t>
+          <t>1,24; 2,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,7</t>
+          <t>0,89; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,37</t>
+          <t>1,41; 2,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,6</t>
+          <t>1,88; 2,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,9</t>
+          <t>1,26; 1,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,61</t>
+          <t>0,99; 1,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,23</t>
+          <t>1,51; 2,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,34</t>
+          <t>1,76; 2,46</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>57994</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10555; 28109</t>
+          <t>10668; 29419</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7267; 23825</t>
+          <t>7312; 23579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12343; 31653</t>
+          <t>11925; 31071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17558; 38705</t>
+          <t>19368; 42629</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5361; 18579</t>
+          <t>4787; 17222</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8024; 23397</t>
+          <t>7720; 24036</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9760; 26235</t>
+          <t>9902; 25469</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19669; 36847</t>
+          <t>21924; 39503</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18699; 39333</t>
+          <t>19014; 39751</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19067; 41166</t>
+          <t>18832; 40343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26173; 51531</t>
+          <t>25890; 51561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41850; 70004</t>
+          <t>45277; 72978</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34862</t>
+          <t>38710</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2011; 11959</t>
+          <t>2805; 12732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12333; 31823</t>
+          <t>12680; 32921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9510; 25614</t>
+          <t>9515; 25169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10206; 26034</t>
+          <t>11518; 28367</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4714; 17275</t>
+          <t>4485; 17478</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3932; 19813</t>
+          <t>3944; 19431</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3921; 15157</t>
+          <t>3860; 15339</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12094; 25970</t>
+          <t>14171; 29682</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8898; 25998</t>
+          <t>8861; 26027</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19085; 42938</t>
+          <t>18904; 43932</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15367; 34450</t>
+          <t>15588; 34434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25536; 47069</t>
+          <t>28349; 51317</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>6488</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3612; 15793</t>
+          <t>3562; 14956</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6457</t>
+          <t>0; 6223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2338; 14886</t>
+          <t>2355; 13707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4805</t>
+          <t>0; 6355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1164; 10627</t>
+          <t>1365; 11083</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1048; 10266</t>
+          <t>1037; 9451</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>954; 8972</t>
+          <t>955; 8753</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1784; 8673</t>
+          <t>1927; 8879</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6925; 21802</t>
+          <t>6907; 21601</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2907; 12309</t>
+          <t>2102; 13022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4513; 18147</t>
+          <t>4654; 18314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1511; 10808</t>
+          <t>3115; 12823</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>20459</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5579; 21746</t>
+          <t>6427; 22236</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6550</t>
+          <t>0; 6224</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4835; 21868</t>
+          <t>4609; 21032</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5285; 21932</t>
+          <t>5050; 22848</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5212; 18458</t>
+          <t>5158; 18524</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6671</t>
+          <t>0; 6636</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6645; 21451</t>
+          <t>6316; 21603</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2892; 16093</t>
+          <t>4778; 16035</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13860; 33759</t>
+          <t>13362; 33638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>954; 9509</t>
+          <t>949; 9502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13598; 35251</t>
+          <t>13937; 36562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10331; 32042</t>
+          <t>11779; 33071</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7522</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6195</t>
+          <t>0; 5832</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2769,59 +2769,59 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2092; 12717</t>
+          <t>2086; 12447</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 4852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1060; 11206</t>
+          <t>1062; 12449</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6669</t>
+          <t>0; 6457</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3323; 15827</t>
+          <t>3117; 15430</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3333; 11740</t>
+          <t>3644; 11316</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1912; 12527</t>
+          <t>1984; 13666</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7715</t>
+          <t>0; 6935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7182; 22975</t>
+          <t>7501; 23173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3720; 13138</t>
+          <t>3996; 12392</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>15006</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 4272</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2000; 15182</t>
+          <t>1969; 13731</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>868; 8456</t>
+          <t>853; 8204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 17821</t>
+          <t>0; 15674</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9494; 25398</t>
+          <t>10151; 27626</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6186; 20525</t>
+          <t>6930; 20651</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9908; 28167</t>
+          <t>9918; 29131</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6123; 18795</t>
+          <t>6714; 21013</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10460; 26643</t>
+          <t>10865; 28018</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11058; 29231</t>
+          <t>10907; 28249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11978; 32518</t>
+          <t>11144; 31808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7971; 28542</t>
+          <t>7827; 26382</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>76135</t>
+          <t>82135</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>135541</t>
+          <t>146179</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34226; 61826</t>
+          <t>33932; 61771</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31544; 62169</t>
+          <t>31004; 59965</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46136; 79126</t>
+          <t>46924; 80278</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42903; 79946</t>
+          <t>48951; 84370</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41157; 72498</t>
+          <t>41874; 70515</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30899; 59842</t>
+          <t>31320; 59318</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47980; 83256</t>
+          <t>49377; 82416</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>59086; 92920</t>
+          <t>68216; 99070</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>83215; 125992</t>
+          <t>83549; 125206</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69874; 111509</t>
+          <t>68692; 107944</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>106136; 153681</t>
+          <t>104211; 152111</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>112580; 162361</t>
+          <t>124303; 173623</t>
         </is>
       </c>
     </row>
